--- a/AtchisonRegime/Outputs/USA/USA500_Real_Estate/df_regTrendSummaryUSA500_Real_Estate.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500_Real_Estate/df_regTrendSummaryUSA500_Real_Estate.xlsx
@@ -714,13 +714,13 @@
         <v>45138</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2378260967038175</v>
+        <v>0.2936011062148047</v>
       </c>
     </row>
   </sheetData>
